--- a/Results/Two_Datasets_Assessment/Mushroom/Tables/generator_summary.xlsx
+++ b/Results/Two_Datasets_Assessment/Mushroom/Tables/generator_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,11 @@
           <t>OverallScore_Formatted</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Rank_Formatted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -493,13 +498,13 @@
         <v>0.6854540568620545</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1712066308380989</v>
+        <v>0.2468983155019921</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8740643163992137</v>
+        <v>0.6501790175485291</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5877629069160155</v>
+        <v>0.5433048226599781</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -511,287 +516,322 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.2469</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>\textbf{0.8741}</t>
+          <t>0.6502</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>\textbf{0.5878}</t>
+          <t>\textbf{0.5433}</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>\textbf{1.0000}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.377432168857154</v>
+        <v>0.3666729230935759</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4593039257982813</v>
+        <v>0.5099445363163269</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5965175288041394</v>
+        <v>0.7325289107288828</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4677193039235878</v>
+        <v>0.5194112033509932</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.3774</t>
+          <t>0.3667</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>\underline{0.4593}</t>
+          <t>0.5099</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.5965</t>
+          <t>\textbf{0.7325}</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>\underline{0.4677}</t>
+          <t>\underline{0.5194}</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>\underline{2.0000}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3666729230935759</v>
+        <v>0.377432168857154</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4039431302146414</v>
+        <v>0.5483620331151577</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6238393249874938</v>
+        <v>0.5651465293055633</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4550039057980709</v>
+        <v>0.4850254362690779</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.3667</t>
+          <t>0.3774</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.4039</t>
+          <t>\textbf{0.5484}</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>\underline{0.6238}</t>
+          <t>0.5651</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.4550</t>
+          <t>0.4850</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3.0000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5100138975778759</v>
+        <v>0.3997825632837796</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2754930305176135</v>
+        <v>0.4937338788414433</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5520664642022749</v>
+        <v>0.580711160887031</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4522734074471169</v>
+        <v>0.4822465372320541</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>\underline{0.5100}</t>
+          <t>0.3998</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.2755</t>
+          <t>0.4937</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.5521</t>
+          <t>0.5807</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.4523</t>
+          <t>0.4822</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4.0000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3363148782492614</v>
+        <v>0.5100138975778759</v>
       </c>
       <c r="D6" t="n">
-        <v>0.343779489884602</v>
+        <v>0.2864860607661532</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4949530413496791</v>
+        <v>0.5187481196936311</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3861457106699889</v>
+        <v>0.4455758131690857</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>\underline{0.5100}</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.3438</t>
+          <t>0.2865</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.4950</t>
+          <t>0.5187</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.3861</t>
+          <t>0.4456</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5.0000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CopulaGAN</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.3997825632837796</v>
+        <v>0.2212644916550226</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3137404995245627</v>
+        <v>0.5100652890254719</v>
       </c>
       <c r="E7" t="n">
-        <v>0.425874725649952</v>
+        <v>0.6793990320601035</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3817975928658662</v>
+        <v>0.4453450929876817</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.3998</t>
+          <t>0.2213</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.3137</t>
+          <t>\underline{0.5101}</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.4259</t>
+          <t>\underline{0.6794}</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.3818</t>
+          <t>0.4453</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6.0000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.2212644916550226</v>
+        <v>0.3363148782492614</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3697079075243822</v>
+        <v>0.4824131139296354</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5898036904498916</v>
+        <v>0.542977064252405</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3763592760542912</v>
+        <v>0.4421430047543167</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.2213</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.3697</t>
+          <t>0.4824</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.5898</t>
+          <t>0.5430</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.3764</t>
+          <t>0.4421</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>7.0000</t>
         </is>
       </c>
     </row>
@@ -808,13 +848,13 @@
         <v>0.1717628035644512</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5327151221325226</v>
+        <v>0.4794436099192703</v>
       </c>
       <c r="E9" t="n">
-        <v>0.25</v>
+        <v>0.2294567983077689</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3035196580655373</v>
+        <v>0.2813752438938922</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
@@ -826,17 +866,22 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>\textbf{0.5327}</t>
+          <t>0.4794</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.2500</t>
+          <t>0.2295</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.3035</t>
+          <t>0.2814</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>8.0000</t>
         </is>
       </c>
     </row>
